--- a/AAII_Financials/Yearly/AILE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AILE_YR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Yearly/AILE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AILE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
   <si>
     <t>AILE</t>
   </si>
@@ -708,26 +708,26 @@
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>420600</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>309200</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>217900</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+        <v>141800</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3"/>
     </row>
@@ -735,17 +735,17 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>132200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>93900</v>
+      </c>
+      <c r="F9" s="3">
+        <v>64800</v>
+      </c>
+      <c r="G9" s="3">
+        <v>41700</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -762,17 +762,17 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>288400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>215300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>153000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>100100</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -802,17 +802,17 @@
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>128500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>97400</v>
+      </c>
+      <c r="F12" s="3">
+        <v>70900</v>
+      </c>
+      <c r="G12" s="3">
+        <v>50900</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -857,25 +857,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>14100</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3"/>
     </row>
@@ -884,10 +884,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -921,16 +921,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5500</v>
+        <v>401600</v>
       </c>
       <c r="E17" s="3">
-        <v>1600</v>
+        <v>297200</v>
       </c>
       <c r="F17" s="3">
-        <v>3900</v>
+        <v>210200</v>
       </c>
       <c r="G17" s="3">
-        <v>0</v>
+        <v>133800</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -947,17 +947,17 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>19000</v>
       </c>
       <c r="E18" s="3">
-        <v>-1600</v>
+        <v>11900</v>
       </c>
       <c r="F18" s="3">
-        <v>-3900</v>
+        <v>7700</v>
       </c>
       <c r="G18" s="3">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -987,17 +987,17 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>800</v>
       </c>
       <c r="E20" s="3">
-        <v>15800</v>
+        <v>-200</v>
       </c>
       <c r="F20" s="3">
-        <v>8700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1015,16 +1015,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>18300</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>12200</v>
       </c>
       <c r="F21" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="H21" s="3">
         <v>0</v>
@@ -1042,25 +1042,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>1100</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3"/>
     </row>
@@ -1069,16 +1069,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-5300</v>
+        <v>-2300</v>
       </c>
       <c r="E23" s="3">
-        <v>14300</v>
+        <v>5500</v>
       </c>
       <c r="F23" s="3">
-        <v>4800</v>
+        <v>2600</v>
       </c>
       <c r="G23" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1096,16 +1096,16 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>600</v>
+        <v>2200</v>
       </c>
       <c r="E24" s="3">
-        <v>800</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+        <v>-6000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1150,16 +1150,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-5800</v>
+        <v>-4400</v>
       </c>
       <c r="E26" s="3">
-        <v>13500</v>
+        <v>11500</v>
       </c>
       <c r="F26" s="3">
-        <v>4800</v>
+        <v>2500</v>
       </c>
       <c r="G26" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1177,16 +1177,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-5800</v>
+        <v>-4400</v>
       </c>
       <c r="E27" s="3">
-        <v>13500</v>
+        <v>8100</v>
       </c>
       <c r="F27" s="3">
-        <v>4800</v>
+        <v>2200</v>
       </c>
       <c r="G27" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1311,17 +1311,17 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-800</v>
       </c>
       <c r="E32" s="3">
-        <v>-15800</v>
+        <v>200</v>
       </c>
       <c r="F32" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1339,16 +1339,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-5800</v>
+        <v>-4400</v>
       </c>
       <c r="E33" s="3">
-        <v>13500</v>
+        <v>11500</v>
       </c>
       <c r="F33" s="3">
-        <v>4800</v>
+        <v>2500</v>
       </c>
       <c r="G33" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1393,16 +1393,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-5800</v>
+        <v>-4400</v>
       </c>
       <c r="E35" s="3">
-        <v>13500</v>
+        <v>11500</v>
       </c>
       <c r="F35" s="3">
-        <v>4800</v>
+        <v>2500</v>
       </c>
       <c r="G35" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1478,16 +1478,16 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>100</v>
+        <v>4800</v>
       </c>
       <c r="E41" s="3">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="F41" s="3">
-        <v>300</v>
-      </c>
-      <c r="G41" s="3">
-        <v>0</v>
+        <v>4400</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1532,25 +1532,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>74000</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>44100</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>33000</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3"/>
     </row>
@@ -1558,26 +1558,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3"/>
     </row>
@@ -1585,14 +1585,14 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>100</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F45" s="3">
-        <v>500</v>
+        <v>1900</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
@@ -1613,16 +1613,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>300</v>
+        <v>80800</v>
       </c>
       <c r="E46" s="3">
-        <v>200</v>
+        <v>45100</v>
       </c>
       <c r="F46" s="3">
-        <v>800</v>
-      </c>
-      <c r="G46" s="3">
-        <v>0</v>
+        <v>39400</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1639,14 +1639,14 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>46700</v>
-      </c>
-      <c r="E47" s="3">
-        <v>290700</v>
-      </c>
-      <c r="F47" s="3">
-        <v>287500</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -1666,26 +1666,26 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3"/>
     </row>
@@ -1705,14 +1705,14 @@
       <c r="G49" s="3">
         <v>0</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3"/>
     </row>
@@ -1774,17 +1774,17 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1500</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
+        <v>600</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -1829,16 +1829,16 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>47000</v>
+        <v>105300</v>
       </c>
       <c r="E54" s="3">
-        <v>291000</v>
+        <v>63500</v>
       </c>
       <c r="F54" s="3">
-        <v>288300</v>
-      </c>
-      <c r="G54" s="3">
-        <v>100</v>
+        <v>40700</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -1882,13 +1882,13 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4100</v>
+        <v>3800</v>
       </c>
       <c r="E57" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="F57" s="3">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -1909,16 +1909,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4800</v>
+        <v>10500</v>
       </c>
       <c r="E58" s="3">
-        <v>1500</v>
+        <v>8100</v>
       </c>
       <c r="F58" s="3">
-        <v>800</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
+        <v>3500</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -1936,16 +1936,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4000</v>
+        <v>4600</v>
       </c>
       <c r="E59" s="3">
-        <v>400</v>
+        <v>3200</v>
       </c>
       <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>100</v>
+        <v>1800</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -1963,16 +1963,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>12900</v>
+        <v>23200</v>
       </c>
       <c r="E60" s="3">
-        <v>2900</v>
+        <v>15300</v>
       </c>
       <c r="F60" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G60" s="3">
-        <v>100</v>
+        <v>8600</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -1990,13 +1990,13 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>91400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>57200</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>54400</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2020,10 +2020,10 @@
         <v>11900</v>
       </c>
       <c r="E62" s="3">
-        <v>10200</v>
+        <v>7800</v>
       </c>
       <c r="F62" s="3">
-        <v>22100</v>
+        <v>6900</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -2125,16 +2125,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>24700</v>
+        <v>126500</v>
       </c>
       <c r="E66" s="3">
-        <v>13100</v>
+        <v>80300</v>
       </c>
       <c r="F66" s="3">
-        <v>24000</v>
-      </c>
-      <c r="G66" s="3">
-        <v>100</v>
+        <v>69800</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2273,16 +2273,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-24500</v>
+        <v>-57600</v>
       </c>
       <c r="E72" s="3">
-        <v>-12500</v>
+        <v>-53200</v>
       </c>
       <c r="F72" s="3">
-        <v>-23200</v>
-      </c>
-      <c r="G72" s="3">
-        <v>0</v>
+        <v>-64600</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2381,16 +2381,16 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>22300</v>
+        <v>-21200</v>
       </c>
       <c r="E76" s="3">
-        <v>277800</v>
+        <v>-16800</v>
       </c>
       <c r="F76" s="3">
-        <v>264300</v>
-      </c>
-      <c r="G76" s="3">
-        <v>0</v>
+        <v>-29100</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2467,16 +2467,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-5800</v>
+        <v>-4400</v>
       </c>
       <c r="E81" s="3">
-        <v>13500</v>
+        <v>11500</v>
       </c>
       <c r="F81" s="3">
-        <v>4800</v>
+        <v>2500</v>
       </c>
       <c r="G81" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2507,25 +2507,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3"/>
     </row>
@@ -2669,16 +2669,16 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-3500</v>
+        <v>-16200</v>
       </c>
       <c r="E89" s="3">
-        <v>-1600</v>
+        <v>-8900</v>
       </c>
       <c r="F89" s="3">
-        <v>-2400</v>
+        <v>-8200</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -2711,23 +2711,23 @@
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3"/>
     </row>
@@ -2790,13 +2790,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>247500</v>
+        <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="F94" s="3">
-        <v>-287500</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -2938,16 +2938,16 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-244000</v>
+        <v>22100</v>
       </c>
       <c r="E100" s="3">
-        <v>800</v>
+        <v>5200</v>
       </c>
       <c r="F100" s="3">
-        <v>290200</v>
+        <v>6700</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -2964,26 +2964,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3"/>
     </row>
@@ -2992,25 +2992,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="E102" s="3">
-        <v>-100</v>
+        <v>-3600</v>
       </c>
       <c r="F102" s="3">
-        <v>200</v>
+        <v>-1500</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>5900</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3"/>
     </row>
